--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>4.036371627883571</v>
+        <v>0.6559103895310803</v>
       </c>
       <c r="D2" t="n">
-        <v>4.468195712896184</v>
+        <v>0.72608180334563</v>
       </c>
       <c r="E2" t="n">
-        <v>13.13703565081731</v>
+        <v>2.134768293257813</v>
       </c>
       <c r="F2" t="n">
-        <v>13.03936128774233</v>
+        <v>2.118896209258128</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.89883057130908</v>
+        <v>5.996059967837725</v>
       </c>
       <c r="D3" t="n">
-        <v>37.08689156563045</v>
+        <v>6.026619879414949</v>
       </c>
       <c r="E3" t="n">
-        <v>13.13703565081731</v>
+        <v>2.134768293257813</v>
       </c>
       <c r="F3" t="n">
-        <v>13.03936128774233</v>
+        <v>2.118896209258128</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>7.875672193296387</v>
+        <v>1.279796731410663</v>
       </c>
       <c r="D4" t="n">
-        <v>8.21092673955421</v>
+        <v>1.334275595177559</v>
       </c>
       <c r="E4" t="n">
-        <v>13.13703565081731</v>
+        <v>2.134768293257813</v>
       </c>
       <c r="F4" t="n">
-        <v>13.03936128774233</v>
+        <v>2.118896209258128</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.554353862461909</v>
+        <v>1.39008250265006</v>
       </c>
       <c r="D5" t="n">
-        <v>9.031757971842101</v>
+        <v>1.467660670424341</v>
       </c>
       <c r="E5" t="n">
-        <v>13.13703565081731</v>
+        <v>2.134768293257813</v>
       </c>
       <c r="F5" t="n">
-        <v>13.03936128774233</v>
+        <v>2.118896209258128</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
